--- a/nn-avito/avito.xlsx
+++ b/nn-avito/avito.xlsx
@@ -947,7 +947,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/6f9ba66ffe0bbc5a.jpg?v=9d934c92cb|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/black-2.jpg?v=6e9a6c9f7a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/black.jpg?v=3b8b6f7c30</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/6f9ba66ffe0bbc5a.jpg?v=d3cef72c0c|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/black-2.jpg?v=6e9a6c9f7a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/black.jpg?v=3b8b6f7c30</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/48916d1f3afb4980.jpg?v=0b78bd84b7|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/black-2.jpg?v=6e9a6c9f7a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/black.jpg?v=3b8b6f7c30</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/48916d1f3afb4980.jpg?v=c774ea2457|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/black-2.jpg?v=6e9a6c9f7a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/black.jpg?v=3b8b6f7c30</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/dd37d2f74dc64ae1.jpg?v=276d3b0516|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/black-2.jpg?v=6e9a6c9f7a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/black.jpg?v=3b8b6f7c30</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/dd37d2f74dc64ae1.jpg?v=1bc10d1115|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/black-2.jpg?v=6e9a6c9f7a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/black.jpg?v=3b8b6f7c30</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/82b570489d856b6e.jpg?v=0a2b6b2187|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/lavender.jpg?v=7d421b119e</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/82b570489d856b6e.jpg?v=63016c5d7c|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/lavender.jpg?v=7d421b119e</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/b2a60f5e0ac124a8.jpg?v=41ae413cb8|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/lavender.jpg?v=7d421b119e</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/b2a60f5e0ac124a8.jpg?v=8c0c0f9b68|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/lavender.jpg?v=7d421b119e</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/5ece202ab773bdd4.jpg?v=de1fa1e1d4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/lavender.jpg?v=7d421b119e</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/5ece202ab773bdd4.jpg?v=ae7f62c8a4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/lavender.jpg?v=7d421b119e</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/ddefb2db88df89b4.jpg?v=494601f50d|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/mist-blue-2.jpg?v=8cab7cca84|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/mist-blue.jpg?v=ab05f3a6b7</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/ddefb2db88df89b4.jpg?v=ba8f98b7ee|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/mist-blue-2.jpg?v=8cab7cca84|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/mist-blue.jpg?v=ab05f3a6b7</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/0faba62fc93a5a6a.jpg?v=2690272d94|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/mist-blue-2.jpg?v=8cab7cca84|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/mist-blue.jpg?v=ab05f3a6b7</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/0faba62fc93a5a6a.jpg?v=b70dc252ec|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/mist-blue-2.jpg?v=8cab7cca84|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/mist-blue.jpg?v=ab05f3a6b7</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/6e9893cd9fc1580c.jpg?v=9591637268|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/mist-blue-2.jpg?v=8cab7cca84|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/mist-blue.jpg?v=ab05f3a6b7</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/6e9893cd9fc1580c.jpg?v=81ca1480cd|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/mist-blue-2.jpg?v=8cab7cca84|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/mist-blue.jpg?v=ab05f3a6b7</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/ca9344246dd4da71.jpg?v=184d49b497|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/sage.jpg?v=1b0499f9ea</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/ca9344246dd4da71.jpg?v=7e52b2b343|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/sage.jpg?v=1b0499f9ea</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/51b5215ffae996b0.jpg?v=3617cfe75e|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/sage.jpg?v=1b0499f9ea</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/51b5215ffae996b0.jpg?v=3a17528dfc|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/sage.jpg?v=1b0499f9ea</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/feaf6e13d79bb7f3.jpg?v=1a40c2fe3a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/sage.jpg?v=1b0499f9ea</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/feaf6e13d79bb7f3.jpg?v=1aa33441ce|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/sage.jpg?v=1b0499f9ea</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/19214383ba879fd4.jpg?v=1a6579430f|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/white-2.jpg?v=667ac4f5fe|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/white.jpg?v=f132cf2c6f</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/19214383ba879fd4.jpg?v=73a6a3dc0d|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/white-2.jpg?v=667ac4f5fe|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/white.jpg?v=f132cf2c6f</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/90c3eba302d68c5f.jpg?v=f614d8cc67|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/white-2.jpg?v=667ac4f5fe|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/white.jpg?v=f132cf2c6f</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/90c3eba302d68c5f.jpg?v=ab69935218|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/white-2.jpg?v=667ac4f5fe|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/white.jpg?v=f132cf2c6f</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/114b106ed4cfc89d.jpg?v=4009435af8|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/white-2.jpg?v=667ac4f5fe|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/white.jpg?v=f132cf2c6f</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/114b106ed4cfc89d.jpg?v=278ef3cbdd|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/white-2.jpg?v=667ac4f5fe|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/white.jpg?v=f132cf2c6f</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/49af4a41be935eba.jpg?v=9bf1f95ed8|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/black-2.jpg?v=6e9a6c9f7a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/black.jpg?v=3b8b6f7c30</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/49af4a41be935eba.jpg?v=3688001c65|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/black-2.jpg?v=6e9a6c9f7a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/black.jpg?v=3b8b6f7c30</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/dd8d68b09166e2e1.jpg?v=993cd41713|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/black-2.jpg?v=6e9a6c9f7a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/black.jpg?v=3b8b6f7c30</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/dd8d68b09166e2e1.jpg?v=9331254e0b|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/black-2.jpg?v=6e9a6c9f7a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/black.jpg?v=3b8b6f7c30</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/37be8730ebba65c3.jpg?v=74c65cc720|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/black-2.jpg?v=6e9a6c9f7a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/black.jpg?v=3b8b6f7c30</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/37be8730ebba65c3.jpg?v=fc90e46a40|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/black-2.jpg?v=6e9a6c9f7a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/black.jpg?v=3b8b6f7c30</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/db3deb16a1065d04.jpg?v=98953bc624|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/lavender.jpg?v=7d421b119e</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/db3deb16a1065d04.jpg?v=4856d634a2|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/lavender.jpg?v=7d421b119e</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/5a3055530b9cec8b.jpg?v=4604b24901|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/lavender.jpg?v=7d421b119e</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/5a3055530b9cec8b.jpg?v=58283078d0|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/lavender.jpg?v=7d421b119e</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/a1c944674541c62e.jpg?v=72ae5c3cfc|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/lavender.jpg?v=7d421b119e</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/a1c944674541c62e.jpg?v=ffa8822354|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/lavender.jpg?v=7d421b119e</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/4dfc5c0b6681de4d.jpg?v=f53385af58|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/mist-blue-2.jpg?v=8cab7cca84|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/mist-blue.jpg?v=ab05f3a6b7</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/4dfc5c0b6681de4d.jpg?v=d80280494c|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/mist-blue-2.jpg?v=8cab7cca84|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/mist-blue.jpg?v=ab05f3a6b7</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/74c0caa3055d70ab.jpg?v=1ebb050b20|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/mist-blue-2.jpg?v=8cab7cca84|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/mist-blue.jpg?v=ab05f3a6b7</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/74c0caa3055d70ab.jpg?v=e532e42bc6|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/mist-blue-2.jpg?v=8cab7cca84|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/mist-blue.jpg?v=ab05f3a6b7</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/da23b6fc0ba70d9b.jpg?v=2874204c71|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/sage.jpg?v=1b0499f9ea</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/da23b6fc0ba70d9b.jpg?v=db82455b66|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/sage.jpg?v=1b0499f9ea</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/1035083af8614077.jpg?v=7044109236|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/sage.jpg?v=1b0499f9ea</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/1035083af8614077.jpg?v=1c8fa946d6|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/sage.jpg?v=1b0499f9ea</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/cd9c7e13e1ee5375.jpg?v=f12a9cf53b|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/sage.jpg?v=1b0499f9ea</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/cd9c7e13e1ee5375.jpg?v=baec89279f|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/sage.jpg?v=1b0499f9ea</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/8a56b3e1f5a7cc4c.jpg?v=ba1fb4d2cc|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/white-2.jpg?v=667ac4f5fe|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/white.jpg?v=f132cf2c6f</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/8a56b3e1f5a7cc4c.jpg?v=d8a298d0dd|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/white-2.jpg?v=667ac4f5fe|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/white.jpg?v=f132cf2c6f</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/a5cdee9c6cc2ce02.jpg?v=1263919890|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/white-2.jpg?v=667ac4f5fe|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/white.jpg?v=f132cf2c6f</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/a5cdee9c6cc2ce02.jpg?v=4ece6cc682|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/white-2.jpg?v=667ac4f5fe|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17/white.jpg?v=f132cf2c6f</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/9b5593e02fcf28d1.jpg?v=7cbc5f296a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/cosmic-orange-2.jpg?v=f5c7a8f7e3|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/cosmic-orange.jpg?v=1d23a64537</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/9b5593e02fcf28d1.jpg?v=cc04bc0675|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/cosmic-orange-2.jpg?v=f5c7a8f7e3|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/cosmic-orange.jpg?v=1d23a64537</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/35b6d1836435cbcf.jpg?v=963f2bfa10|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/cosmic-orange-2.jpg?v=f5c7a8f7e3|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/cosmic-orange.jpg?v=1d23a64537</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/35b6d1836435cbcf.jpg?v=f76b357b80|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/cosmic-orange-2.jpg?v=f5c7a8f7e3|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/cosmic-orange.jpg?v=1d23a64537</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/fe74479ed0a02aa0.jpg?v=fdfeb87f5c|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/cosmic-orange-2.jpg?v=f5c7a8f7e3|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/cosmic-orange.jpg?v=1d23a64537</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/fe74479ed0a02aa0.jpg?v=47dcb7d35e|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/cosmic-orange-2.jpg?v=f5c7a8f7e3|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/cosmic-orange.jpg?v=1d23a64537</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/7bb5cd34009f5407.jpg?v=80b1b1066f|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/deep-blue-2.jpg?v=b73092a0c4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/deep-blue.jpg?v=050c49dcf9</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/7bb5cd34009f5407.jpg?v=21f8a2d116|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/deep-blue-2.jpg?v=b73092a0c4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/deep-blue.jpg?v=050c49dcf9</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/84dc6f3a277547c9.jpg?v=e4e411b16a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/deep-blue-2.jpg?v=b73092a0c4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/deep-blue.jpg?v=050c49dcf9</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/84dc6f3a277547c9.jpg?v=f31815575f|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/deep-blue-2.jpg?v=b73092a0c4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/deep-blue.jpg?v=050c49dcf9</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/6d4433034cafbbc7.jpg?v=23dfb246a8|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/deep-blue-2.jpg?v=b73092a0c4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/deep-blue.jpg?v=050c49dcf9</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/6d4433034cafbbc7.jpg?v=8d635fa5cc|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/deep-blue-2.jpg?v=b73092a0c4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/deep-blue.jpg?v=050c49dcf9</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/6008301450086ec0.jpg?v=d667462631|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/silver-2.jpg?v=92aa8ff8e4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/silver.jpg?v=1f32c2c9dd</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/6008301450086ec0.jpg?v=93b93fabd7|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/silver-2.jpg?v=92aa8ff8e4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/silver.jpg?v=1f32c2c9dd</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/139f1c1aa8c8d6d7.jpg?v=f4abe73404|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/silver-2.jpg?v=92aa8ff8e4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/silver.jpg?v=1f32c2c9dd</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/139f1c1aa8c8d6d7.jpg?v=72c401e351|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/silver-2.jpg?v=92aa8ff8e4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/silver.jpg?v=1f32c2c9dd</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/75fc272faa8951e7.jpg?v=4e648e3d81|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/silver-2.jpg?v=92aa8ff8e4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/silver.jpg?v=1f32c2c9dd</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/75fc272faa8951e7.jpg?v=db079ca64c|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/silver-2.jpg?v=92aa8ff8e4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/silver.jpg?v=1f32c2c9dd</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/a64b6f74d190254e.jpg?v=1fbcc861e3|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/cosmic-orange-2.jpg?v=f5c7a8f7e3|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/cosmic-orange.jpg?v=1d23a64537</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/a64b6f74d190254e.jpg?v=db2b89064e|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/cosmic-orange-2.jpg?v=f5c7a8f7e3|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/cosmic-orange.jpg?v=1d23a64537</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/fb52885bd22735d1.jpg?v=e9b7d2c8a7|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/cosmic-orange-2.jpg?v=f5c7a8f7e3|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/cosmic-orange.jpg?v=1d23a64537</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/fb52885bd22735d1.jpg?v=ef643e89e7|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/cosmic-orange-2.jpg?v=f5c7a8f7e3|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/cosmic-orange.jpg?v=1d23a64537</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/02ab0f6ae5669391.jpg?v=dc2582f3ba|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/cosmic-orange-2.jpg?v=f5c7a8f7e3|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/cosmic-orange.jpg?v=1d23a64537</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/02ab0f6ae5669391.jpg?v=6219e81c5b|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/cosmic-orange-2.jpg?v=f5c7a8f7e3|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/cosmic-orange.jpg?v=1d23a64537</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/8fa8589ccf8fd956.jpg?v=94eb3cc8b6|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/deep-blue-2.jpg?v=b73092a0c4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/deep-blue.jpg?v=050c49dcf9</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/8fa8589ccf8fd956.jpg?v=ce2144807e|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/deep-blue-2.jpg?v=b73092a0c4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/deep-blue.jpg?v=050c49dcf9</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/73c19b332853eb21.jpg?v=b6439b86d9|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/deep-blue-2.jpg?v=b73092a0c4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/deep-blue.jpg?v=050c49dcf9</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/73c19b332853eb21.jpg?v=56dd0da8f0|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/deep-blue-2.jpg?v=b73092a0c4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/deep-blue.jpg?v=050c49dcf9</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/baeb7c93a0db9db2.jpg?v=9119f5ae35|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/deep-blue-2.jpg?v=b73092a0c4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/deep-blue.jpg?v=050c49dcf9</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/baeb7c93a0db9db2.jpg?v=c3d6bf7c0b|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/deep-blue-2.jpg?v=b73092a0c4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/deep-blue.jpg?v=050c49dcf9</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/3e444517516e5d80.jpg?v=fd6ea55aeb|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/silver-2.jpg?v=92aa8ff8e4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/silver.jpg?v=1f32c2c9dd</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/3e444517516e5d80.jpg?v=80ddfd863d|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/silver-2.jpg?v=92aa8ff8e4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/silver.jpg?v=1f32c2c9dd</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/d1bb525923ffced6.jpg?v=638cd2e655|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/silver-2.jpg?v=92aa8ff8e4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/silver.jpg?v=1f32c2c9dd</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/d1bb525923ffced6.jpg?v=6e9de5c560|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/silver-2.jpg?v=92aa8ff8e4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/silver.jpg?v=1f32c2c9dd</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/462d046eef547418.jpg?v=a11eb55b59|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/cosmic-orange-2.jpg?v=f5c7a8f7e3|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/cosmic-orange.jpg?v=1d23a64537</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/462d046eef547418.jpg?v=133d172743|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/cosmic-orange-2.jpg?v=f5c7a8f7e3|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/cosmic-orange.jpg?v=1d23a64537</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/6071327a2be2970d.jpg?v=8dc795272d|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/cosmic-orange-2.jpg?v=f5c7a8f7e3|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/cosmic-orange.jpg?v=1d23a64537</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/6071327a2be2970d.jpg?v=1ea32f5244|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/cosmic-orange-2.jpg?v=f5c7a8f7e3|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/cosmic-orange.jpg?v=1d23a64537</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/72b7337da5c8fe91.jpg?v=a8c8c99b29|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/cosmic-orange-2.jpg?v=f5c7a8f7e3|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/cosmic-orange.jpg?v=1d23a64537</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/72b7337da5c8fe91.jpg?v=7df4ed504a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/cosmic-orange-2.jpg?v=f5c7a8f7e3|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/cosmic-orange.jpg?v=1d23a64537</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/d7a80ff89b747109.jpg?v=904c225989|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/deep-blue-2.jpg?v=b73092a0c4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/deep-blue.jpg?v=050c49dcf9</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/d7a80ff89b747109.jpg?v=4ebbce4d57|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/deep-blue-2.jpg?v=b73092a0c4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/deep-blue.jpg?v=050c49dcf9</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/a564c2bf2d388589.jpg?v=4690508ae0|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/deep-blue-2.jpg?v=b73092a0c4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/deep-blue.jpg?v=050c49dcf9</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/a564c2bf2d388589.jpg?v=0f1eea842c|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/deep-blue-2.jpg?v=b73092a0c4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/deep-blue.jpg?v=050c49dcf9</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/0e0dcdb976877f1e.jpg?v=30f8d35f93|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/deep-blue-2.jpg?v=b73092a0c4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/deep-blue.jpg?v=050c49dcf9</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/0e0dcdb976877f1e.jpg?v=192a00fdff|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/deep-blue-2.jpg?v=b73092a0c4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/deep-blue.jpg?v=050c49dcf9</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/9c215b964f1b08cd.jpg?v=a5357a63de|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/silver-2.jpg?v=92aa8ff8e4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/silver.jpg?v=1f32c2c9dd</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/9c215b964f1b08cd.jpg?v=95bd6cbcd7|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/silver-2.jpg?v=92aa8ff8e4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/silver.jpg?v=1f32c2c9dd</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/df4dd8c5c9f2b9fc.jpg?v=ee1f9503bd|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/silver-2.jpg?v=92aa8ff8e4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/silver.jpg?v=1f32c2c9dd</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/df4dd8c5c9f2b9fc.jpg?v=dbacc82a0e|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/silver-2.jpg?v=92aa8ff8e4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/silver.jpg?v=1f32c2c9dd</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/87848ec15e240c6e.jpg?v=fb87ee2f9a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/silver-2.jpg?v=92aa8ff8e4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/silver.jpg?v=1f32c2c9dd</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/87848ec15e240c6e.jpg?v=11a4d84604|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/silver-2.jpg?v=92aa8ff8e4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro/silver.jpg?v=1f32c2c9dd</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/a22cbd1ad95a9796.jpg?v=284a325ca1|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/cosmic-orange-2.jpg?v=b6615ef9d8|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/cosmic-orange.jpg?v=57064daf2a</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/a22cbd1ad95a9796.jpg?v=532e73603a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/cosmic-orange-2.jpg?v=b6615ef9d8|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/cosmic-orange.jpg?v=57064daf2a</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/2c0e9b08d17c7f16.jpg?v=131920b9d3|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/cosmic-orange-2.jpg?v=b6615ef9d8|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/cosmic-orange.jpg?v=57064daf2a</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/2c0e9b08d17c7f16.jpg?v=be850f53b5|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/cosmic-orange-2.jpg?v=b6615ef9d8|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/cosmic-orange.jpg?v=57064daf2a</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/483b72a3f885aaef.jpg?v=53f389aa35|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/cosmic-orange-2.jpg?v=b6615ef9d8|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/cosmic-orange.jpg?v=57064daf2a</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/483b72a3f885aaef.jpg?v=924b0fd9fb|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/cosmic-orange-2.jpg?v=b6615ef9d8|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/cosmic-orange.jpg?v=57064daf2a</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/657982f39974a8aa.jpg?v=9849df778d|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/deep-blue-2.jpg?v=67df02a01a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/deep-blue.jpg?v=b848f3451b</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/657982f39974a8aa.jpg?v=5bdc471a12|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/deep-blue-2.jpg?v=67df02a01a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/deep-blue.jpg?v=b848f3451b</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/21c096e839ce4151.jpg?v=ff683b3e8e|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/deep-blue-2.jpg?v=67df02a01a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/deep-blue.jpg?v=b848f3451b</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/21c096e839ce4151.jpg?v=5478577093|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/deep-blue-2.jpg?v=67df02a01a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/deep-blue.jpg?v=b848f3451b</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/aabbab3ba9353613.jpg?v=bec529b37c|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/deep-blue-2.jpg?v=67df02a01a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/deep-blue.jpg?v=b848f3451b</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/aabbab3ba9353613.jpg?v=065c2d898a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/deep-blue-2.jpg?v=67df02a01a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/deep-blue.jpg?v=b848f3451b</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/f04a30e20707818a.jpg?v=cbc0897e62|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/silver-2.jpg?v=25f0e7a1f4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/silver.jpg?v=f00c09fbc9</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/f04a30e20707818a.jpg?v=ad9e1f9a77|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/silver-2.jpg?v=25f0e7a1f4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/silver.jpg?v=f00c09fbc9</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -6864,7 +6864,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/a967b7f79a9ca5cf.jpg?v=12b98b99d0|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/silver-2.jpg?v=25f0e7a1f4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/silver.jpg?v=f00c09fbc9</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/a967b7f79a9ca5cf.jpg?v=9affd53614|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/silver-2.jpg?v=25f0e7a1f4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/silver.jpg?v=f00c09fbc9</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/3f91fc4a9a59640c.jpg?v=a9796e92d0|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/silver-2.jpg?v=25f0e7a1f4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/silver.jpg?v=f00c09fbc9</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/3f91fc4a9a59640c.jpg?v=f7922ffc96|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/silver-2.jpg?v=25f0e7a1f4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/silver.jpg?v=f00c09fbc9</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/9028a0879d11fa07.jpg?v=9fa3797212|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/cosmic-orange-2.jpg?v=b6615ef9d8|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/cosmic-orange.jpg?v=57064daf2a</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/9028a0879d11fa07.jpg?v=7f3edfa0ac|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/cosmic-orange-2.jpg?v=b6615ef9d8|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/cosmic-orange.jpg?v=57064daf2a</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/dc2c81096bdb97a7.jpg?v=ce92480b20|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/cosmic-orange-2.jpg?v=b6615ef9d8|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/cosmic-orange.jpg?v=57064daf2a</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/dc2c81096bdb97a7.jpg?v=4367e6c27c|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/cosmic-orange-2.jpg?v=b6615ef9d8|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/cosmic-orange.jpg?v=57064daf2a</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/9d8baebbbd8066ab.jpg?v=b810fa7d22|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/cosmic-orange-2.jpg?v=b6615ef9d8|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/cosmic-orange.jpg?v=57064daf2a</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/9d8baebbbd8066ab.jpg?v=43cd23bf80|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/cosmic-orange-2.jpg?v=b6615ef9d8|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/cosmic-orange.jpg?v=57064daf2a</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/5e7abfea9807da86.jpg?v=665aa3aaa4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/deep-blue-2.jpg?v=67df02a01a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/deep-blue.jpg?v=b848f3451b</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/5e7abfea9807da86.jpg?v=683db4389f|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/deep-blue-2.jpg?v=67df02a01a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/deep-blue.jpg?v=b848f3451b</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/ce54897d1a9b76a8.jpg?v=d30e890ad9|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/deep-blue-2.jpg?v=67df02a01a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/deep-blue.jpg?v=b848f3451b</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/ce54897d1a9b76a8.jpg?v=84813a62da|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/deep-blue-2.jpg?v=67df02a01a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/deep-blue.jpg?v=b848f3451b</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/19872964e0acf4c0.jpg?v=d61e818037|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/deep-blue-2.jpg?v=67df02a01a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/deep-blue.jpg?v=b848f3451b</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/19872964e0acf4c0.jpg?v=b3467d4429|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/deep-blue-2.jpg?v=67df02a01a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/deep-blue.jpg?v=b848f3451b</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -7640,7 +7640,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/f302e293ddbb8be5.jpg?v=589c659d0e|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/silver-2.jpg?v=25f0e7a1f4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/silver.jpg?v=f00c09fbc9</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/f302e293ddbb8be5.jpg?v=22c0bc291d|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/silver-2.jpg?v=25f0e7a1f4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/silver.jpg?v=f00c09fbc9</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/4209de95eebcea47.jpg?v=577df4a5af|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/silver-2.jpg?v=25f0e7a1f4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/silver.jpg?v=f00c09fbc9</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/4209de95eebcea47.jpg?v=133acfc94f|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/silver-2.jpg?v=25f0e7a1f4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/silver.jpg?v=f00c09fbc9</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -7834,7 +7834,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/8f438b3844df519a.jpg?v=711377c4ef|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/silver-2.jpg?v=25f0e7a1f4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/silver.jpg?v=f00c09fbc9</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/8f438b3844df519a.jpg?v=29ab727f5e|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/silver-2.jpg?v=25f0e7a1f4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/silver.jpg?v=f00c09fbc9</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -7931,7 +7931,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/7b94e47f8e4f75f9.jpg?v=3712344550|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/cosmic-orange-2.jpg?v=b6615ef9d8|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/cosmic-orange.jpg?v=57064daf2a</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/7b94e47f8e4f75f9.jpg?v=687ecf946c|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/cosmic-orange-2.jpg?v=b6615ef9d8|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/cosmic-orange.jpg?v=57064daf2a</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/01950a869e4c7434.jpg?v=8e16a7b1c3|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/cosmic-orange-2.jpg?v=b6615ef9d8|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/cosmic-orange.jpg?v=57064daf2a</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/01950a869e4c7434.jpg?v=993fae1fac|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/cosmic-orange-2.jpg?v=b6615ef9d8|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/cosmic-orange.jpg?v=57064daf2a</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -8125,7 +8125,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/6f132c81358af4d6.jpg?v=417ad39bbe|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/cosmic-orange-2.jpg?v=b6615ef9d8|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/cosmic-orange.jpg?v=57064daf2a</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/6f132c81358af4d6.jpg?v=8f23a33001|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/cosmic-orange-2.jpg?v=b6615ef9d8|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/cosmic-orange.jpg?v=57064daf2a</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -8222,7 +8222,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/f3d6612daaf18c37.jpg?v=558a13d1cd|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/deep-blue-2.jpg?v=67df02a01a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/deep-blue.jpg?v=b848f3451b</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/f3d6612daaf18c37.jpg?v=a54fa5b3ee|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/deep-blue-2.jpg?v=67df02a01a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/deep-blue.jpg?v=b848f3451b</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -8319,7 +8319,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/30c95254aba61e26.jpg?v=3530ed1756|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/deep-blue-2.jpg?v=67df02a01a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/deep-blue.jpg?v=b848f3451b</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/30c95254aba61e26.jpg?v=ea197a14bc|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/deep-blue-2.jpg?v=67df02a01a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/deep-blue.jpg?v=b848f3451b</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/b187b9c33bbc7511.jpg?v=b5f39ef15f|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/deep-blue-2.jpg?v=67df02a01a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/deep-blue.jpg?v=b848f3451b</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/b187b9c33bbc7511.jpg?v=eb1aed6cd4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/deep-blue-2.jpg?v=67df02a01a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/deep-blue.jpg?v=b848f3451b</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -8513,7 +8513,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/88002feb8b73b741.jpg?v=c3a69e2abe|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/silver-2.jpg?v=25f0e7a1f4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/silver.jpg?v=f00c09fbc9</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/88002feb8b73b741.jpg?v=d6d3434093|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/silver-2.jpg?v=25f0e7a1f4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/silver.jpg?v=f00c09fbc9</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/8c6d8d4935b0ce80.jpg?v=41924c1381|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/silver-2.jpg?v=25f0e7a1f4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/silver.jpg?v=f00c09fbc9</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/8c6d8d4935b0ce80.jpg?v=8bf1834be3|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/silver-2.jpg?v=25f0e7a1f4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/silver.jpg?v=f00c09fbc9</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -8707,7 +8707,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/79a6e18b068ec0b2.jpg?v=98f0d4ca9d|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/silver-2.jpg?v=25f0e7a1f4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/silver.jpg?v=f00c09fbc9</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/79a6e18b068ec0b2.jpg?v=4e14eeb2fe|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/silver-2.jpg?v=25f0e7a1f4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/silver.jpg?v=f00c09fbc9</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -8804,7 +8804,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/f65c179e4b3d50aa.jpg?v=8e9d6b6217|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/cosmic-orange-2.jpg?v=b6615ef9d8|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/cosmic-orange.jpg?v=57064daf2a</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/f65c179e4b3d50aa.jpg?v=8b412a256d|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/cosmic-orange-2.jpg?v=b6615ef9d8|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/cosmic-orange.jpg?v=57064daf2a</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/d2000e609e3ed490.jpg?v=a03f2cc582|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/cosmic-orange-2.jpg?v=b6615ef9d8|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/cosmic-orange.jpg?v=57064daf2a</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/d2000e609e3ed490.jpg?v=fe9b041267|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/cosmic-orange-2.jpg?v=b6615ef9d8|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/cosmic-orange.jpg?v=57064daf2a</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/611c95387122a4c0.jpg?v=73a3e8646e|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/deep-blue-2.jpg?v=67df02a01a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/deep-blue.jpg?v=b848f3451b</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/611c95387122a4c0.jpg?v=96182d5049|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/deep-blue-2.jpg?v=67df02a01a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/deep-blue.jpg?v=b848f3451b</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/445ce52f2aacc5be.jpg?v=9842d5d2dd|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/deep-blue-2.jpg?v=67df02a01a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/deep-blue.jpg?v=b848f3451b</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/445ce52f2aacc5be.jpg?v=bfd3df110c|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/deep-blue-2.jpg?v=67df02a01a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/deep-blue.jpg?v=b848f3451b</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -9192,7 +9192,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/33bffe76024f87cb.jpg?v=f3bde9f972|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/silver-2.jpg?v=25f0e7a1f4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/silver.jpg?v=f00c09fbc9</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/33bffe76024f87cb.jpg?v=f430940099|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/silver-2.jpg?v=25f0e7a1f4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/silver.jpg?v=f00c09fbc9</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/b8153133f79dfe1c.jpg?v=e349ca336e|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/silver-2.jpg?v=25f0e7a1f4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/silver.jpg?v=f00c09fbc9</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/b8153133f79dfe1c.jpg?v=fdb577f2db|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/silver-2.jpg?v=25f0e7a1f4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17-pro-max/silver.jpg?v=f00c09fbc9</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/78d23a5e3028fdc7.jpg?v=7a6779c829|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17e/black-2.jpg?v=3ed3e287fa</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/78d23a5e3028fdc7.jpg?v=77e081ca10|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17e/black-2.jpg?v=3ed3e287fa</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -9483,7 +9483,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/e8771378780fdb4c.jpg?v=63b3820634|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17e/black-2.jpg?v=3ed3e287fa</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/e8771378780fdb4c.jpg?v=744ec0c45f|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17e/black-2.jpg?v=3ed3e287fa</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -9580,7 +9580,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/7c454e93d7f2a7fb.jpg?v=4db693471c|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17e/black-2.jpg?v=3ed3e287fa</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/7c454e93d7f2a7fb.jpg?v=9a0125caca|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17e/black-2.jpg?v=3ed3e287fa</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/fa390d68867a3cfc.jpg?v=9855fecd3e|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17e/pink-2.jpg?v=4af79b5888</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/fa390d68867a3cfc.jpg?v=1037ee0604|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17e/pink-2.jpg?v=4af79b5888</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/db57b0cee052545e.jpg?v=51a7ddca58|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17e/pink-2.jpg?v=4af79b5888</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/db57b0cee052545e.jpg?v=5786423ab0|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17e/pink-2.jpg?v=4af79b5888</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -9871,7 +9871,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/a9e67ed039dc1ba3.jpg?v=3285525b8e|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17e/pink-2.jpg?v=4af79b5888</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/a9e67ed039dc1ba3.jpg?v=04ea4716cd|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17e/pink-2.jpg?v=4af79b5888</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/c598449606833583.jpg?v=12b82d7fdb|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17e/white-2.jpg?v=8dc59539ee</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/c598449606833583.jpg?v=633dffaacf|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17e/white-2.jpg?v=8dc59539ee</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/f5c8ca5c917d1c87.jpg?v=c23961a4be|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17e/white-2.jpg?v=8dc59539ee</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/f5c8ca5c917d1c87.jpg?v=dcc29dfe92|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17e/white-2.jpg?v=8dc59539ee</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -10162,7 +10162,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/431a46cc5d7cc6a6.jpg?v=c86e16099c|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17e/white-2.jpg?v=8dc59539ee</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/431a46cc5d7cc6a6.jpg?v=07fc0ea3c0|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17e/white-2.jpg?v=8dc59539ee</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -10259,7 +10259,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/5ce7cc09b2f9f6fa.jpg?v=5cd58130dc|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17e/black-2.jpg?v=3ed3e287fa</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/5ce7cc09b2f9f6fa.jpg?v=78a2404524|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17e/black-2.jpg?v=3ed3e287fa</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -10356,7 +10356,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/b85174b363ee9479.jpg?v=b246beef8a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17e/black-2.jpg?v=3ed3e287fa</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/b85174b363ee9479.jpg?v=9b727bfe4b|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17e/black-2.jpg?v=3ed3e287fa</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -10453,7 +10453,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/c497622931dd7a96.jpg?v=2bd16735f7|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17e/pink-2.jpg?v=4af79b5888</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/c497622931dd7a96.jpg?v=7a3c54fb77|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17e/pink-2.jpg?v=4af79b5888</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -10550,7 +10550,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/1b8599ae3b63e56f.jpg?v=84d3448e90|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17e/pink-2.jpg?v=4af79b5888</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/1b8599ae3b63e56f.jpg?v=bd66f83304|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17e/pink-2.jpg?v=4af79b5888</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/a4efddc68ec7a488.jpg?v=2de823a4a2|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17e/white-2.jpg?v=8dc59539ee</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/a4efddc68ec7a488.jpg?v=ac853a9d07|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17e/white-2.jpg?v=8dc59539ee</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -10744,7 +10744,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/4a6e1bdc9df8e0c0.jpg?v=2917d546cc|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17e/white-2.jpg?v=8dc59539ee</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/4a6e1bdc9df8e0c0.jpg?v=68152a4f58|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-17e/white-2.jpg?v=8dc59539ee</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/dd58289b85361635.jpg?v=3929f3fb52|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/cloud-white-2.jpg?v=e2e599d9b9|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/cloud-white.jpg?v=5a4ab1ed94</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/dd58289b85361635.jpg?v=44e43349f8|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/cloud-white-2.jpg?v=e2e599d9b9|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/cloud-white.jpg?v=5a4ab1ed94</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -10938,7 +10938,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/d256e12dcbaab841.jpg?v=6ed3b35337|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/cloud-white-2.jpg?v=e2e599d9b9|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/cloud-white.jpg?v=5a4ab1ed94</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/d256e12dcbaab841.jpg?v=5909079e1d|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/cloud-white-2.jpg?v=e2e599d9b9|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/cloud-white.jpg?v=5a4ab1ed94</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -11035,7 +11035,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/b445178d40779fc9.jpg?v=a95f11ed94|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/light-gold-2.jpg?v=5d9be7ccef|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/light-gold.jpg?v=4e3e8a9169</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/b445178d40779fc9.jpg?v=40db266bde|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/light-gold-2.jpg?v=5d9be7ccef|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/light-gold.jpg?v=4e3e8a9169</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -11132,7 +11132,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/8f35225b6697f36e.jpg?v=5e824a2ce8|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/light-gold-2.jpg?v=5d9be7ccef|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/light-gold.jpg?v=4e3e8a9169</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/8f35225b6697f36e.jpg?v=b48fd2136f|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/light-gold-2.jpg?v=5d9be7ccef|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/light-gold.jpg?v=4e3e8a9169</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -11229,7 +11229,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/c22711fc9bf1ae05.jpg?v=0d77038440|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/sky-blue-2.jpg?v=719bfad913|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/sky-blue.jpg?v=2925915a56</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/c22711fc9bf1ae05.jpg?v=57c8abd109|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/sky-blue-2.jpg?v=719bfad913|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/sky-blue.jpg?v=2925915a56</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -11326,7 +11326,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/14bd72a42ed0020d.jpg?v=1222913cf5|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/sky-blue-2.jpg?v=719bfad913|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/sky-blue.jpg?v=2925915a56</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/14bd72a42ed0020d.jpg?v=897d7f98b9|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/sky-blue-2.jpg?v=719bfad913|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/sky-blue.jpg?v=2925915a56</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -11423,7 +11423,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/6744381016bc6079.jpg?v=7b25ce595e|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/space-black-2.jpg?v=075c409c50|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/space-black.jpg?v=37353739e1</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/6744381016bc6079.jpg?v=374b979321|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/space-black-2.jpg?v=075c409c50|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/space-black.jpg?v=37353739e1</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -11520,7 +11520,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/31d4000409fd3a51.jpg?v=352a45d24f|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/space-black-2.jpg?v=075c409c50|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/space-black.jpg?v=37353739e1</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/31d4000409fd3a51.jpg?v=dc84ece7f9|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/space-black-2.jpg?v=075c409c50|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/space-black.jpg?v=37353739e1</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/0b7770d9fb512faf.jpg?v=09323c637f|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/cloud-white-2.jpg?v=e2e599d9b9|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/cloud-white.jpg?v=5a4ab1ed94</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/0b7770d9fb512faf.jpg?v=8793bc0846|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/cloud-white-2.jpg?v=e2e599d9b9|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/cloud-white.jpg?v=5a4ab1ed94</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -11714,7 +11714,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/f0c437f3f37327cf.jpg?v=40240c701f|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/light-gold-2.jpg?v=5d9be7ccef|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/light-gold.jpg?v=4e3e8a9169</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/f0c437f3f37327cf.jpg?v=21bf47d350|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/light-gold-2.jpg?v=5d9be7ccef|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/light-gold.jpg?v=4e3e8a9169</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -11811,7 +11811,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/9e942ae82b897915.jpg?v=d569719e4d|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/light-gold-2.jpg?v=5d9be7ccef|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/light-gold.jpg?v=4e3e8a9169</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/9e942ae82b897915.jpg?v=09fbe20bdd|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/light-gold-2.jpg?v=5d9be7ccef|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/light-gold.jpg?v=4e3e8a9169</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -11908,7 +11908,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/064ce8af9d11f781.jpg?v=d2e42fd033|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/sky-blue-2.jpg?v=719bfad913|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/sky-blue.jpg?v=2925915a56</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/064ce8af9d11f781.jpg?v=bc8b9ecc14|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/sky-blue-2.jpg?v=719bfad913|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/sky-blue.jpg?v=2925915a56</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/c3f267b98af69d13.jpg?v=e7736aa7eb|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/sky-blue-2.jpg?v=719bfad913|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/sky-blue.jpg?v=2925915a56</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/c3f267b98af69d13.jpg?v=164aad1804|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/sky-blue-2.jpg?v=719bfad913|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/sky-blue.jpg?v=2925915a56</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -12102,7 +12102,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/998dda6b8ed963d1.jpg?v=0b8e4e3a47|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/space-black-2.jpg?v=075c409c50|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/space-black.jpg?v=37353739e1</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/998dda6b8ed963d1.jpg?v=48ec99d321|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/space-black-2.jpg?v=075c409c50|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/space-black.jpg?v=37353739e1</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -12199,7 +12199,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/9e4d3f95aa18f4ea.jpg?v=5399d33bb4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/space-black-2.jpg?v=075c409c50|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/space-black.jpg?v=37353739e1</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/9e4d3f95aa18f4ea.jpg?v=ae84281575|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/space-black-2.jpg?v=075c409c50|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/space-black.jpg?v=37353739e1</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -12296,7 +12296,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/53221e59ad1d2f4b.jpg?v=338613147d|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/cloud-white-2.jpg?v=e2e599d9b9|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/cloud-white.jpg?v=5a4ab1ed94</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/53221e59ad1d2f4b.jpg?v=fb4167e4e5|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/cloud-white-2.jpg?v=e2e599d9b9|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/cloud-white.jpg?v=5a4ab1ed94</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/bb11e1745d423f82.jpg?v=825579d0e3|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/light-gold-2.jpg?v=5d9be7ccef|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/light-gold.jpg?v=4e3e8a9169</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/bb11e1745d423f82.jpg?v=c2fa2ab76b|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/light-gold-2.jpg?v=5d9be7ccef|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/light-gold.jpg?v=4e3e8a9169</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -12490,7 +12490,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/6d685da30b9f17df.jpg?v=f6e17f10fb|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/light-gold-2.jpg?v=5d9be7ccef|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/light-gold.jpg?v=4e3e8a9169</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/6d685da30b9f17df.jpg?v=f0871157e8|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/light-gold-2.jpg?v=5d9be7ccef|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/light-gold.jpg?v=4e3e8a9169</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -12587,7 +12587,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/5e2fe8b0217ded71.jpg?v=de5faf29c8|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/sky-blue-2.jpg?v=719bfad913|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/sky-blue.jpg?v=2925915a56</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/5e2fe8b0217ded71.jpg?v=decf5eb5bf|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/sky-blue-2.jpg?v=719bfad913|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/sky-blue.jpg?v=2925915a56</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/b33a5a41a2726d8f.jpg?v=c838f602f7|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/space-black-2.jpg?v=075c409c50|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/space-black.jpg?v=37353739e1</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/b33a5a41a2726d8f.jpg?v=90537ad778|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/space-black-2.jpg?v=075c409c50|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-air/space-black.jpg?v=37353739e1</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -12781,7 +12781,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/34aef3dd4b80465e.jpg?v=f19b762c0a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/black-2.jpg?v=9555264f4a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/black.jpg?v=98e4b031c8</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/34aef3dd4b80465e.jpg?v=83afe7732a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/black-2.jpg?v=9555264f4a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/black.jpg?v=98e4b031c8</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -12878,7 +12878,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/9a982d0d8470d34d.jpg?v=7f5c49f556|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/black-2.jpg?v=9555264f4a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/black.jpg?v=98e4b031c8</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/9a982d0d8470d34d.jpg?v=40a219f886|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/black-2.jpg?v=9555264f4a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/black.jpg?v=98e4b031c8</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -12975,7 +12975,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/34cd25bf4f537c65.jpg?v=ccaf67f696|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/pink-2.jpg?v=95f29dea03|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/pink.jpg?v=12cd3710e7</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/34cd25bf4f537c65.jpg?v=cf966ce01b|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/pink-2.jpg?v=95f29dea03|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/pink.jpg?v=12cd3710e7</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -13072,7 +13072,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/bf5b8dc0e14a44c5.jpg?v=8179e32007|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/teal-2.jpg?v=50e70ac936|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/teal.jpg?v=961cc391d2</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/bf5b8dc0e14a44c5.jpg?v=5764d3ef66|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/teal-2.jpg?v=50e70ac936|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/teal.jpg?v=961cc391d2</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -13169,7 +13169,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/0f55ef7f9d36865b.jpg?v=014ed6b243|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/teal-2.jpg?v=50e70ac936|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/teal.jpg?v=961cc391d2</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/0f55ef7f9d36865b.jpg?v=cd9bee5408|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/teal-2.jpg?v=50e70ac936|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/teal.jpg?v=961cc391d2</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/4798ba639b4fba62.jpg?v=c3c9be016b|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/ultramarine-2.jpg?v=7588a4df34|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/ultramarine.jpg?v=d9a5c4d60e</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/4798ba639b4fba62.jpg?v=fbc5bbf5b0|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/ultramarine-2.jpg?v=7588a4df34|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/ultramarine.jpg?v=d9a5c4d60e</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -13363,7 +13363,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/f115addd8fa57494.jpg?v=782b8ff110|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/ultramarine-2.jpg?v=7588a4df34|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/ultramarine.jpg?v=d9a5c4d60e</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/f115addd8fa57494.jpg?v=2300574b82|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/ultramarine-2.jpg?v=7588a4df34|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/ultramarine.jpg?v=d9a5c4d60e</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -13460,7 +13460,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/db2686847e0748e2.jpg?v=7606db08c3|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/white-2.jpg?v=88dfe22697|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/white.jpg?v=796da39c93</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/db2686847e0748e2.jpg?v=21ae3e1269|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/white-2.jpg?v=88dfe22697|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/white.jpg?v=796da39c93</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -13557,7 +13557,7 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/106806ad9ac472c6.jpg?v=f371620551|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/black-2.jpg?v=9555264f4a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/black.jpg?v=98e4b031c8</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/106806ad9ac472c6.jpg?v=f86af8f3ca|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/black-2.jpg?v=9555264f4a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/black.jpg?v=98e4b031c8</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -13654,7 +13654,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/426944f26fd48a54.jpg?v=c85b3edf19|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/pink-2.jpg?v=95f29dea03|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/pink.jpg?v=12cd3710e7</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/426944f26fd48a54.jpg?v=7b5070e1a0|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/pink-2.jpg?v=95f29dea03|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/pink.jpg?v=12cd3710e7</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -13751,7 +13751,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/dff9e406848c472e.jpg?v=fb0a0e6422|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/teal-2.jpg?v=50e70ac936|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/teal.jpg?v=961cc391d2</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/dff9e406848c472e.jpg?v=88d17c4443|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/teal-2.jpg?v=50e70ac936|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/teal.jpg?v=961cc391d2</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/8637d1a3e05104f2.jpg?v=72f394fb1f|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/ultramarine-2.jpg?v=7588a4df34|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/ultramarine.jpg?v=d9a5c4d60e</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/8637d1a3e05104f2.jpg?v=1db7880a9b|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/ultramarine-2.jpg?v=7588a4df34|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/ultramarine.jpg?v=d9a5c4d60e</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -13945,7 +13945,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/d857f3d2c9fbff49.jpg?v=28ea7af22a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/white-2.jpg?v=88dfe22697|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/white.jpg?v=796da39c93</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/d857f3d2c9fbff49.jpg?v=a0668c29eb|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/white-2.jpg?v=88dfe22697|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/white.jpg?v=796da39c93</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/eaafdb874d06c48b.jpg?v=9fc890d013|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/black-2.jpg?v=9555264f4a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/black.jpg?v=98e4b031c8</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/eaafdb874d06c48b.jpg?v=7b99f491d9|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/black-2.jpg?v=9555264f4a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/black.jpg?v=98e4b031c8</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -14139,7 +14139,7 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/74fb74c0f61e71bb.jpg?v=738052eb22|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/pink-2.jpg?v=95f29dea03|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/pink.jpg?v=12cd3710e7</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/74fb74c0f61e71bb.jpg?v=d207f95d6c|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/pink-2.jpg?v=95f29dea03|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/pink.jpg?v=12cd3710e7</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -14236,7 +14236,7 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/56a1fe74a22b493e.jpg?v=66c476c9e0|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/teal-2.jpg?v=50e70ac936|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/teal.jpg?v=961cc391d2</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/56a1fe74a22b493e.jpg?v=ec8bf03c07|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/teal-2.jpg?v=50e70ac936|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/teal.jpg?v=961cc391d2</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -14333,7 +14333,7 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/c4e7ba1ebbee9576.jpg?v=871f86eedf|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/ultramarine-2.jpg?v=7588a4df34|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/ultramarine.jpg?v=d9a5c4d60e</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/c4e7ba1ebbee9576.jpg?v=37c69adc85|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/ultramarine-2.jpg?v=7588a4df34|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16/ultramarine.jpg?v=d9a5c4d60e</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -14430,7 +14430,7 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/b84df61ac779d046.jpg?v=452821ca56|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/black-2.jpg?v=ff7771f4c8|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/black.jpg?v=448aac5493</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/b84df61ac779d046.jpg?v=20a50652b7|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/black-2.jpg?v=ff7771f4c8|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/black.jpg?v=448aac5493</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -14527,7 +14527,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/ec14f0aaef4db880.jpg?v=f1bd80fd97|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/black-2.jpg?v=ff7771f4c8|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/black.jpg?v=448aac5493</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/ec14f0aaef4db880.jpg?v=2d38936009|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/black-2.jpg?v=ff7771f4c8|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/black.jpg?v=448aac5493</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -14624,7 +14624,7 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/fba02e7df3372560.jpg?v=c922732662|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/pink-2.jpg?v=0518e192f4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/pink.jpg?v=63c6f39c05</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/fba02e7df3372560.jpg?v=3d9f7fa4db|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/pink-2.jpg?v=0518e192f4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/pink.jpg?v=63c6f39c05</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -14721,7 +14721,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/e4180f18af6e86ef.jpg?v=56fb67aba2|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/teal-2.jpg?v=6afd182913|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/teal.jpg?v=ff59c7527d</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/e4180f18af6e86ef.jpg?v=0dc270d0ec|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/teal-2.jpg?v=6afd182913|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/teal.jpg?v=ff59c7527d</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -14818,7 +14818,7 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/c1160d92cbcb48e8.jpg?v=eab55ce335|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/ultramarine-2.jpg?v=658adb1e42|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/ultramarine.jpg?v=641ca66963</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/c1160d92cbcb48e8.jpg?v=c6de437f84|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/ultramarine-2.jpg?v=658adb1e42|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/ultramarine.jpg?v=641ca66963</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -14915,7 +14915,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/936af4070973335e.jpg?v=81cdf2b59e|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/white-2.jpg?v=9b944261bb|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/white.jpg?v=0652866e96</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/936af4070973335e.jpg?v=728415fbd8|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/white-2.jpg?v=9b944261bb|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/white.jpg?v=0652866e96</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -15012,7 +15012,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/e59e2c1103e19699.jpg?v=e8803ed936|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/black-2.jpg?v=ff7771f4c8|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/black.jpg?v=448aac5493</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/e59e2c1103e19699.jpg?v=8de9d393d6|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/black-2.jpg?v=ff7771f4c8|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/black.jpg?v=448aac5493</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -15109,7 +15109,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/8bbcf14656a8dd68.jpg?v=61a78999b4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/pink-2.jpg?v=0518e192f4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/pink.jpg?v=63c6f39c05</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/8bbcf14656a8dd68.jpg?v=41f31f9f79|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/pink-2.jpg?v=0518e192f4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/pink.jpg?v=63c6f39c05</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -15206,7 +15206,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/c568458df206fade.jpg?v=b2676589ab|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/teal-2.jpg?v=6afd182913|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/teal.jpg?v=ff59c7527d</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/c568458df206fade.jpg?v=687c8763e3|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/teal-2.jpg?v=6afd182913|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/teal.jpg?v=ff59c7527d</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -15303,7 +15303,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/22e7f3623d273b55.jpg?v=bf82aae92b|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/ultramarine-2.jpg?v=658adb1e42|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/ultramarine.jpg?v=641ca66963</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/22e7f3623d273b55.jpg?v=f38f9cad33|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/ultramarine-2.jpg?v=658adb1e42|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/ultramarine.jpg?v=641ca66963</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -15400,7 +15400,7 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/925f153d9ed1789f.jpg?v=41d915e0c1|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/white-2.jpg?v=9b944261bb|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/white.jpg?v=0652866e96</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/925f153d9ed1789f.jpg?v=3987a70326|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/white-2.jpg?v=9b944261bb|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/white.jpg?v=0652866e96</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -15497,7 +15497,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/705a609944f6c65c.jpg?v=cb12c1b108|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/black-2.jpg?v=ff7771f4c8|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/black.jpg?v=448aac5493</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/705a609944f6c65c.jpg?v=86a382d747|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/black-2.jpg?v=ff7771f4c8|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/black.jpg?v=448aac5493</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -15594,7 +15594,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/fd8112393d19e379.jpg?v=c01fbdb497|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/pink-2.jpg?v=0518e192f4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/pink.jpg?v=63c6f39c05</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/fd8112393d19e379.jpg?v=62ebc31bd6|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/pink-2.jpg?v=0518e192f4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/pink.jpg?v=63c6f39c05</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -15691,7 +15691,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/65e23883cb4718a0.jpg?v=67f026860d|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/teal-2.jpg?v=6afd182913|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/teal.jpg?v=ff59c7527d</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/65e23883cb4718a0.jpg?v=724be4bc74|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/teal-2.jpg?v=6afd182913|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/teal.jpg?v=ff59c7527d</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -15788,7 +15788,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/32ddb456347e0899.jpg?v=0dfdae922f|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/ultramarine-2.jpg?v=658adb1e42|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/ultramarine.jpg?v=641ca66963</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/32ddb456347e0899.jpg?v=40d474b01f|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/ultramarine-2.jpg?v=658adb1e42|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/ultramarine.jpg?v=641ca66963</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -15885,7 +15885,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/b5824fb71a813bbb.jpg?v=0a2c4bb59f|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/white-2.jpg?v=9b944261bb|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/white.jpg?v=0652866e96</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/b5824fb71a813bbb.jpg?v=91e2c542fe|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/white-2.jpg?v=9b944261bb|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/white.jpg?v=0652866e96</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -15982,7 +15982,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/c6b84dad7a828bbb.jpg?v=6e441ce086|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/white-2.jpg?v=9b944261bb|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/white.jpg?v=0652866e96</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/c6b84dad7a828bbb.jpg?v=a261bccab2|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/white-2.jpg?v=9b944261bb|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-plus/white.jpg?v=0652866e96</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -16079,7 +16079,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/d83e83187d737b60.jpg?v=a15172edeb|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/black.jpg?v=fc52657721</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/d83e83187d737b60.jpg?v=d007cd74bf|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/black.jpg?v=fc52657721</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -16176,7 +16176,7 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/34ff66f0feaf3fc0.jpg?v=637c74ce60|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/black.jpg?v=fc52657721</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/34ff66f0feaf3fc0.jpg?v=421cc6f2c9|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/black.jpg?v=fc52657721</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -16273,7 +16273,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/bba145f33fa04638.jpg?v=0e399b0a0a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/desert-titanium-2.jpg?v=38d1eb4a43|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/desert-titanium.jpg?v=8461301608</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/bba145f33fa04638.jpg?v=8096bb3e2a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/desert-titanium-2.jpg?v=38d1eb4a43|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/desert-titanium.jpg?v=8461301608</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -16370,7 +16370,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/62d028108489ad04.jpg?v=4416c77c94|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/desert-titanium-2.jpg?v=38d1eb4a43|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/desert-titanium.jpg?v=8461301608</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/62d028108489ad04.jpg?v=5d0f74707e|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/desert-titanium-2.jpg?v=38d1eb4a43|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/desert-titanium.jpg?v=8461301608</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
@@ -16467,7 +16467,7 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/36dacbb8206a8870.jpg?v=486fea4eda|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/desert-titanium-2.jpg?v=38d1eb4a43|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/desert-titanium.jpg?v=8461301608</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/36dacbb8206a8870.jpg?v=cf5ac41966|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/desert-titanium-2.jpg?v=38d1eb4a43|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/desert-titanium.jpg?v=8461301608</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
@@ -16564,7 +16564,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/df6c8f913748ecd6.jpg?v=53fc9f1aef|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/natural-titanium-2.jpg?v=e21d71d7f3|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/natural-titanium.jpg?v=cb92473bf4</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/df6c8f913748ecd6.jpg?v=32d51d2bfc|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/natural-titanium-2.jpg?v=e21d71d7f3|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/natural-titanium.jpg?v=cb92473bf4</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -16661,7 +16661,7 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/ec64f1f79bae387e.jpg?v=9798cf268e|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/natural-titanium-2.jpg?v=e21d71d7f3|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/natural-titanium.jpg?v=cb92473bf4</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/ec64f1f79bae387e.jpg?v=1148a9df72|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/natural-titanium-2.jpg?v=e21d71d7f3|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/natural-titanium.jpg?v=cb92473bf4</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -16758,7 +16758,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/06f36338423638ea.jpg?v=2f39c381ef|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/natural-titanium-2.jpg?v=e21d71d7f3|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/natural-titanium.jpg?v=cb92473bf4</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/06f36338423638ea.jpg?v=7915d6fa45|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/natural-titanium-2.jpg?v=e21d71d7f3|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/natural-titanium.jpg?v=cb92473bf4</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -16855,7 +16855,7 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/9f747f35dee57ce8.jpg?v=e1d58463b1|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/white.jpg?v=c2b582d99d</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/9f747f35dee57ce8.jpg?v=7f9587b35d|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/white.jpg?v=c2b582d99d</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
@@ -16952,7 +16952,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/975ee8b830e9d700.jpg?v=63e83e5bc9|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/white.jpg?v=c2b582d99d</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/975ee8b830e9d700.jpg?v=0806dae0a2|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/white.jpg?v=c2b582d99d</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -17049,7 +17049,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/08d848aa7fab7031.jpg?v=56360af468|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/black.jpg?v=fc52657721</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/08d848aa7fab7031.jpg?v=8ecb0bd831|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/black.jpg?v=fc52657721</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
@@ -17146,7 +17146,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/8778663c3d6c90ef.jpg?v=a338c6836c|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/desert-titanium-2.jpg?v=38d1eb4a43|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/desert-titanium.jpg?v=8461301608</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/8778663c3d6c90ef.jpg?v=0618f382f0|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/desert-titanium-2.jpg?v=38d1eb4a43|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/desert-titanium.jpg?v=8461301608</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -17243,7 +17243,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/d7926bdcfff1df31.jpg?v=85fab9ba34|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/desert-titanium-2.jpg?v=38d1eb4a43|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/desert-titanium.jpg?v=8461301608</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/d7926bdcfff1df31.jpg?v=2ef84a3170|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/desert-titanium-2.jpg?v=38d1eb4a43|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/desert-titanium.jpg?v=8461301608</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -17340,7 +17340,7 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/11d57c7b370905f8.jpg?v=1a30fbfcfd|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/natural-titanium-2.jpg?v=e21d71d7f3|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/natural-titanium.jpg?v=cb92473bf4</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/11d57c7b370905f8.jpg?v=3db0ad74e5|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/natural-titanium-2.jpg?v=e21d71d7f3|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/natural-titanium.jpg?v=cb92473bf4</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -17437,7 +17437,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/63139f76cea9b70b.jpg?v=a17b2168e9|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/white.jpg?v=c2b582d99d</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/63139f76cea9b70b.jpg?v=97fbbc6f26|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/white.jpg?v=c2b582d99d</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -17534,7 +17534,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/253296f5eb849263.jpg?v=66a20ec686|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/white.jpg?v=c2b582d99d</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/253296f5eb849263.jpg?v=9c37eadeda|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/white.jpg?v=c2b582d99d</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -17631,7 +17631,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/25f2f571e0caf1b4.jpg?v=032bb53e5f|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/black.jpg?v=fc52657721</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/25f2f571e0caf1b4.jpg?v=058189df10|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/black.jpg?v=fc52657721</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -17728,7 +17728,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/f06bda2c3ca7054d.jpg?v=b0f1cd7796|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/desert-titanium-2.jpg?v=38d1eb4a43|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/desert-titanium.jpg?v=8461301608</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/f06bda2c3ca7054d.jpg?v=7be67ade95|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/desert-titanium-2.jpg?v=38d1eb4a43|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/desert-titanium.jpg?v=8461301608</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -17825,7 +17825,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/8d82a0d4ec319966.jpg?v=bf2c697e00|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/natural-titanium-2.jpg?v=e21d71d7f3|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/natural-titanium.jpg?v=cb92473bf4</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/8d82a0d4ec319966.jpg?v=a066c6553a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/natural-titanium-2.jpg?v=e21d71d7f3|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/natural-titanium.jpg?v=cb92473bf4</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
@@ -17922,7 +17922,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/03e19a2966b633a3.jpg?v=59d3791cfa|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/white.jpg?v=c2b582d99d</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/03e19a2966b633a3.jpg?v=6235030274|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/white.jpg?v=c2b582d99d</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -18019,7 +18019,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/fe3ddff4c880a9b0.jpg?v=6acdb80180|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/black.jpg?v=fc52657721</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/fe3ddff4c880a9b0.jpg?v=b1b4364567|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/black.jpg?v=fc52657721</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/26a024c220373e44.jpg?v=39524e1f7e|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/desert-titanium-2.jpg?v=38d1eb4a43|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/desert-titanium.jpg?v=8461301608</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/26a024c220373e44.jpg?v=44dbb0bf69|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/desert-titanium-2.jpg?v=38d1eb4a43|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/desert-titanium.jpg?v=8461301608</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -18213,7 +18213,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/5d8792c73c690811.jpg?v=2e31796a70|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/white.jpg?v=c2b582d99d</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/5d8792c73c690811.jpg?v=15ed5240a9|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro/white.jpg?v=c2b582d99d</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -18310,7 +18310,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/91ea37d3ac926b47.jpg?v=46f4558e99|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/black.jpg?v=9390b48646</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/91ea37d3ac926b47.jpg?v=c982f7e439|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/black.jpg?v=9390b48646</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -18407,7 +18407,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/4bf8810d07bef129.jpg?v=a440bb71ed|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/black.jpg?v=9390b48646</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/4bf8810d07bef129.jpg?v=7ece805031|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/black.jpg?v=9390b48646</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
@@ -18504,7 +18504,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/a14fdb7f91f01c13.jpg?v=d543c72821|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/desert-titanium-2.jpg?v=93f9c43b51|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/desert-titanium.jpg?v=81da81e2d6</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/a14fdb7f91f01c13.jpg?v=1e2e954b3d|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/desert-titanium-2.jpg?v=93f9c43b51|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/desert-titanium.jpg?v=81da81e2d6</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -18601,7 +18601,7 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/4812d0ad5b67eff5.jpg?v=f575fa7c52|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/natural-titanium-2.jpg?v=a9e4eae3d4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/natural-titanium.jpg?v=3b611c9a8a</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/4812d0ad5b67eff5.jpg?v=e073e3039f|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/natural-titanium-2.jpg?v=a9e4eae3d4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/natural-titanium.jpg?v=3b611c9a8a</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -18698,7 +18698,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/9941167329212e46.jpg?v=3bae3a8dec|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/natural-titanium-2.jpg?v=a9e4eae3d4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/natural-titanium.jpg?v=3b611c9a8a</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/9941167329212e46.jpg?v=a0e3a63ba5|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/natural-titanium-2.jpg?v=a9e4eae3d4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/natural-titanium.jpg?v=3b611c9a8a</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -18795,7 +18795,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/02e3bcabd61908df.jpg?v=1419b50d1c|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/natural-titanium-2.jpg?v=a9e4eae3d4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/natural-titanium.jpg?v=3b611c9a8a</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/02e3bcabd61908df.jpg?v=c791961a20|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/natural-titanium-2.jpg?v=a9e4eae3d4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/natural-titanium.jpg?v=3b611c9a8a</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -18892,7 +18892,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/857f94bdc0ff7e41.jpg?v=a4737aeffb|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/white.jpg?v=6f7041bf0e</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/857f94bdc0ff7e41.jpg?v=33b2fccf32|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/white.jpg?v=6f7041bf0e</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -18989,7 +18989,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/1144fdb410e46856.jpg?v=865505eff0|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/white.jpg?v=6f7041bf0e</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/1144fdb410e46856.jpg?v=39b21f0a1a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/white.jpg?v=6f7041bf0e</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -19086,7 +19086,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/b0550da4453daf79.jpg?v=54dcf8882b|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/black.jpg?v=9390b48646</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/b0550da4453daf79.jpg?v=88b8de4936|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/black.jpg?v=9390b48646</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -19183,7 +19183,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/261322a45aca67f3.jpg?v=9c806cb575|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/black.jpg?v=9390b48646</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/261322a45aca67f3.jpg?v=3c55939312|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/black.jpg?v=9390b48646</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -19280,7 +19280,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/5b34284e2dc48731.jpg?v=89f874e9e5|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/desert-titanium-2.jpg?v=93f9c43b51|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/desert-titanium.jpg?v=81da81e2d6</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/5b34284e2dc48731.jpg?v=be8da8ec9e|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/desert-titanium-2.jpg?v=93f9c43b51|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/desert-titanium.jpg?v=81da81e2d6</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -19377,7 +19377,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/d10cefabca57e02a.jpg?v=98ad164590|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/desert-titanium-2.jpg?v=93f9c43b51|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/desert-titanium.jpg?v=81da81e2d6</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/d10cefabca57e02a.jpg?v=33250bb19e|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/desert-titanium-2.jpg?v=93f9c43b51|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/desert-titanium.jpg?v=81da81e2d6</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/057bc431c8ed6012.jpg?v=22f58fe7e3|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/natural-titanium-2.jpg?v=a9e4eae3d4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/natural-titanium.jpg?v=3b611c9a8a</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/057bc431c8ed6012.jpg?v=0e65176723|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/natural-titanium-2.jpg?v=a9e4eae3d4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/natural-titanium.jpg?v=3b611c9a8a</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
@@ -19571,7 +19571,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/8974fb102f5e3779.jpg?v=9d06b0f153|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/natural-titanium-2.jpg?v=a9e4eae3d4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/natural-titanium.jpg?v=3b611c9a8a</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/8974fb102f5e3779.jpg?v=4f689e80b6|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/natural-titanium-2.jpg?v=a9e4eae3d4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/natural-titanium.jpg?v=3b611c9a8a</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -19668,7 +19668,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/179235a8de3eaa61.jpg?v=a5c029d2c8|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/white.jpg?v=6f7041bf0e</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/179235a8de3eaa61.jpg?v=f78dea4cb3|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/white.jpg?v=6f7041bf0e</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -19765,7 +19765,7 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/d7eb323319f001d7.jpg?v=a31c42b9c7|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/white.jpg?v=6f7041bf0e</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/d7eb323319f001d7.jpg?v=ddf87af162|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/white.jpg?v=6f7041bf0e</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/77c1262fbd73e290.jpg?v=185c02d80d|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/white.jpg?v=6f7041bf0e</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/77c1262fbd73e290.jpg?v=bd278b4e79|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/white.jpg?v=6f7041bf0e</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -19959,7 +19959,7 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/0d7f6b01ec765207.jpg?v=8d24658cd3|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/black.jpg?v=9390b48646</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/0d7f6b01ec765207.jpg?v=378f439b87|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/black.jpg?v=9390b48646</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -20056,7 +20056,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/638f8b1dd5e236db.jpg?v=8fca1831e3|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/desert-titanium-2.jpg?v=93f9c43b51|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/desert-titanium.jpg?v=81da81e2d6</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/638f8b1dd5e236db.jpg?v=9dfc45cc74|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/desert-titanium-2.jpg?v=93f9c43b51|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/desert-titanium.jpg?v=81da81e2d6</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -20153,7 +20153,7 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/518c85683a44267e.jpg?v=63b421bec6|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/natural-titanium-2.jpg?v=a9e4eae3d4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/natural-titanium.jpg?v=3b611c9a8a</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/518c85683a44267e.jpg?v=5f0428e11f|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/natural-titanium-2.jpg?v=a9e4eae3d4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/natural-titanium.jpg?v=3b611c9a8a</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -20250,7 +20250,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/eac416cd604a0f0b.jpg?v=63261b4304|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/white.jpg?v=6f7041bf0e</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/eac416cd604a0f0b.jpg?v=1513cb243c|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16-pro-max/white.jpg?v=6f7041bf0e</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -20347,7 +20347,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/7e63c584841dca4b.jpg?v=53275d60d1|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16e/black-2.jpg?v=75bd0bb918|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16e/black.jpg?v=e194cb87d8</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/7e63c584841dca4b.jpg?v=88b76580e3|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16e/black-2.jpg?v=75bd0bb918|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16e/black.jpg?v=e194cb87d8</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -20444,7 +20444,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/644dd68b4dde5a12.jpg?v=6bb438a569|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16e/black-2.jpg?v=75bd0bb918|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16e/black.jpg?v=e194cb87d8</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/644dd68b4dde5a12.jpg?v=203c93d83e|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16e/black-2.jpg?v=75bd0bb918|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16e/black.jpg?v=e194cb87d8</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
@@ -20541,7 +20541,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/b254d4f6b70c9d61.jpg?v=1a4630baf8|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16e/white-2.jpg?v=fa197ee635|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16e/white.jpg?v=7f97950237</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/b254d4f6b70c9d61.jpg?v=412db179d6|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16e/white-2.jpg?v=fa197ee635|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16e/white.jpg?v=7f97950237</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -20638,7 +20638,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/228b940e61dc77c3.jpg?v=1db130bc67|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16e/black-2.jpg?v=75bd0bb918|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16e/black.jpg?v=e194cb87d8</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/228b940e61dc77c3.jpg?v=4cad93e46f|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16e/black-2.jpg?v=75bd0bb918|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16e/black.jpg?v=e194cb87d8</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -20735,7 +20735,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/f4d98b79fb8f4a39.jpg?v=3425c53f11|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16e/black-2.jpg?v=75bd0bb918|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16e/black.jpg?v=e194cb87d8</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/f4d98b79fb8f4a39.jpg?v=4a2547d348|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16e/black-2.jpg?v=75bd0bb918|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16e/black.jpg?v=e194cb87d8</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -20832,7 +20832,7 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/8aac5d05e2c269c1.jpg?v=c97a3f107a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16e/white-2.jpg?v=fa197ee635|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16e/white.jpg?v=7f97950237</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/8aac5d05e2c269c1.jpg?v=f459b0ada7|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16e/white-2.jpg?v=fa197ee635|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16e/white.jpg?v=7f97950237</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -20929,7 +20929,7 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/7493a37dec410d0b.jpg?v=2d29d853b5|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16e/white-2.jpg?v=fa197ee635|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16e/white.jpg?v=7f97950237</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/7493a37dec410d0b.jpg?v=065c214635|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16e/white-2.jpg?v=fa197ee635|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16e/white.jpg?v=7f97950237</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -21026,7 +21026,7 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/4af37aca899654ff.jpg?v=796e589cc4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16e/black-2.jpg?v=75bd0bb918|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16e/black.jpg?v=e194cb87d8</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/4af37aca899654ff.jpg?v=45aba35ec1|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16e/black-2.jpg?v=75bd0bb918|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16e/black.jpg?v=e194cb87d8</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -21123,7 +21123,7 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/537e568a53c9007e.jpg?v=0101966df5|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16e/white-2.jpg?v=fa197ee635|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16e/white.jpg?v=7f97950237</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/537e568a53c9007e.jpg?v=51c07aeaf1|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16e/white-2.jpg?v=fa197ee635|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-16e/white.jpg?v=7f97950237</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -21220,7 +21220,7 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/1d3f643ebc713c39.jpg?v=e2df86a475|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-15/black-2.jpg?v=ea3ce46143|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-15/black.jpg?v=1d90070565</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/1d3f643ebc713c39.jpg?v=e015e87166|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-15/black-2.jpg?v=ea3ce46143|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-15/black.jpg?v=1d90070565</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -21317,7 +21317,7 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/a87afba12d7a3705.jpg?v=67299bc62d|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-15/blue-2.jpg?v=c8cba9393a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-15/blue.jpg?v=8edc250597</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/a87afba12d7a3705.jpg?v=46051ff188|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-15/blue-2.jpg?v=c8cba9393a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-15/blue.jpg?v=8edc250597</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
@@ -21414,7 +21414,7 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/8649d7efb29ffb49.jpg?v=839bb51b02|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-15/green-2.jpg?v=49fa62943b|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-15/green.jpg?v=5533996f1a</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/8649d7efb29ffb49.jpg?v=4311e3ea8e|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-15/green-2.jpg?v=49fa62943b|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-15/green.jpg?v=5533996f1a</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
@@ -21511,7 +21511,7 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/3b9da86be476fef9.jpg?v=0d94dd0aa2|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-15/black-2.jpg?v=ea3ce46143|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-15/black.jpg?v=1d90070565</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/3b9da86be476fef9.jpg?v=5dbf6f26f1|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-15/black-2.jpg?v=ea3ce46143|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-15/black.jpg?v=1d90070565</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
@@ -21608,7 +21608,7 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/6072ff94d39f9f47.jpg?v=4041b5845c|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-15/blue-2.jpg?v=c8cba9393a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-15/blue.jpg?v=8edc250597</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/6072ff94d39f9f47.jpg?v=fb33409f0f|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-15/blue-2.jpg?v=c8cba9393a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-15/blue.jpg?v=8edc250597</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
@@ -21705,7 +21705,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/bf757622b6e65823.jpg?v=e97e3fcc2f|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-15-plus/pink-2.jpg?v=34a38f921b|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-15-plus/pink.jpg?v=91e8973564</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/bf757622b6e65823.jpg?v=b3a728fa71|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-15-plus/pink-2.jpg?v=34a38f921b|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-15-plus/pink.jpg?v=91e8973564</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
@@ -21802,7 +21802,7 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/5b41c53571444e95.jpg?v=f77d54a199|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-15-plus/yellow-2.jpg?v=dac5574adf|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-15-plus/yellow.jpg?v=8e5407fa3b</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/5b41c53571444e95.jpg?v=1af7554ddb|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-15-plus/yellow-2.jpg?v=dac5574adf|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-15-plus/yellow.jpg?v=8e5407fa3b</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -21899,7 +21899,7 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/d07456dea6650c14.jpg?v=e5273b4b5a|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-15-pro-max/black.jpg?v=44490a6b94</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/d07456dea6650c14.jpg?v=06490ae9e5|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-15-pro-max/black.jpg?v=44490a6b94</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
@@ -21996,7 +21996,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/cc99792ff452dbfa.jpg?v=ff0d0bc3a8|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-15-pro-max/blue.jpg?v=9b9cbe5bd8</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/cc99792ff452dbfa.jpg?v=4bc8971b74|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-15-pro-max/blue.jpg?v=9b9cbe5bd8</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
@@ -22093,7 +22093,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/37d87ff5c59ad9ab.jpg?v=a75366a246|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-15-pro-max/blue.jpg?v=9b9cbe5bd8</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/37d87ff5c59ad9ab.jpg?v=349b5c3469|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-15-pro-max/blue.jpg?v=9b9cbe5bd8</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
@@ -22190,7 +22190,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/573528b480bee94c.jpg?v=ecdc487dd8|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-15-pro-max/natural-titanium-2.jpg?v=09d74c832d|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-15-pro-max/natural-titanium.jpg?v=dc03873df8</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/573528b480bee94c.jpg?v=084b034e9b|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-15-pro-max/natural-titanium-2.jpg?v=09d74c832d|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-15-pro-max/natural-titanium.jpg?v=dc03873df8</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
@@ -22287,7 +22287,7 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/998ccdee09df7f06.jpg?v=48f0918c73|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-15-pro-max/white.jpg?v=f869c3ff24</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/998ccdee09df7f06.jpg?v=6484bcf427|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-15-pro-max/white.jpg?v=f869c3ff24</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
@@ -22384,7 +22384,7 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/0ff7f0de0e2201fb.jpg?v=04cff6fb18|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14/midnight-2.jpg?v=fd246a7790|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14/midnight.jpg?v=af21befaca</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/0ff7f0de0e2201fb.jpg?v=597e4405a9|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14/midnight-2.jpg?v=fd246a7790|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14/midnight.jpg?v=af21befaca</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -22481,7 +22481,7 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/5944a3c940607fd5.jpg?v=ad8cbbc221|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14/midnight-2.jpg?v=fd246a7790|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14/midnight.jpg?v=af21befaca</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/5944a3c940607fd5.jpg?v=ae0027e101|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14/midnight-2.jpg?v=fd246a7790|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14/midnight.jpg?v=af21befaca</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -22578,7 +22578,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/85bce7a5b9e3c65b.jpg?v=ebf1a96f31|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14/starlight-2.jpg?v=8c3c97101e|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14/starlight.jpg?v=778a3d7803</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/85bce7a5b9e3c65b.jpg?v=8c58ebfec4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14/starlight-2.jpg?v=8c3c97101e|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14/starlight.jpg?v=778a3d7803</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
@@ -22675,7 +22675,7 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/0be53e0cf288e7d0.jpg?v=f25944710b|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14/yellow-2.jpg?v=c559a8e627|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14/yellow.jpg?v=f7dac65ed4</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/0be53e0cf288e7d0.jpg?v=84bc11a550|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14/yellow-2.jpg?v=c559a8e627|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14/yellow.jpg?v=f7dac65ed4</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
@@ -22772,7 +22772,7 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/c67399ad460c7a15.jpg?v=9b6dc868e1|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14/yellow-2.jpg?v=c559a8e627|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14/yellow.jpg?v=f7dac65ed4</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/c67399ad460c7a15.jpg?v=27d46bcf9f|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14/yellow-2.jpg?v=c559a8e627|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14/yellow.jpg?v=f7dac65ed4</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
@@ -22869,7 +22869,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/11f7b72f0818f022.jpg?v=083b19ba95|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14/blue-2.jpg?v=1eac6c1d7b|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14/blue.jpg?v=5fe6c9e1c8</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/11f7b72f0818f022.jpg?v=776df6989f|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14/blue-2.jpg?v=1eac6c1d7b|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14/blue.jpg?v=5fe6c9e1c8</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -22966,7 +22966,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/2e316c65696daf87.jpg?v=38012c43b6|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14/midnight-2.jpg?v=fd246a7790|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14/midnight.jpg?v=af21befaca</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/2e316c65696daf87.jpg?v=5151f9ab36|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14/midnight-2.jpg?v=fd246a7790|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14/midnight.jpg?v=af21befaca</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
@@ -23063,7 +23063,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/399708ccd47de81a.jpg?v=c221f8487b|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14/purple-2.jpg?v=1149fc2172|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14/purple.jpg?v=858f3bacb8</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/399708ccd47de81a.jpg?v=11876d5637|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14/purple-2.jpg?v=1149fc2172|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14/purple.jpg?v=858f3bacb8</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
@@ -23160,7 +23160,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/e7ca96856cbd0d90.jpg?v=88631615e8|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14/red-2.jpg?v=61c11dee0a</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/e7ca96856cbd0d90.jpg?v=5d34c477c9|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14/red-2.jpg?v=61c11dee0a</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
@@ -23257,7 +23257,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/792b6b52f25b3156.jpg?v=9402a86ebe|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14/starlight-2.jpg?v=8c3c97101e|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14/starlight.jpg?v=778a3d7803</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/792b6b52f25b3156.jpg?v=f2a1ec9fc3|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14/starlight-2.jpg?v=8c3c97101e|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14/starlight.jpg?v=778a3d7803</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
@@ -23354,7 +23354,7 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/7c9c3bd44ef093e6.jpg?v=107324d569|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14-plus/blue-2.jpg?v=01e5701e3c|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14-plus/blue.jpg?v=c3307297b9</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/7c9c3bd44ef093e6.jpg?v=6b3faaaade|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14-plus/blue-2.jpg?v=01e5701e3c|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14-plus/blue.jpg?v=c3307297b9</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
@@ -23451,7 +23451,7 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/0289a03255eb8614.jpg?v=814300f722|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14-plus/starlight-2.jpg?v=6fe1ec1bac|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14-plus/starlight.jpg?v=7aebe9ae97</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/0289a03255eb8614.jpg?v=8fc99f6df4|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14-plus/starlight-2.jpg?v=6fe1ec1bac|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14-plus/starlight.jpg?v=7aebe9ae97</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
@@ -23548,7 +23548,7 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/b70aad7b026157d1.jpg?v=ad562b53f2|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14-pro-max/deep-purple.jpg?v=6b5a7bbad0</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/b70aad7b026157d1.jpg?v=c42e03dee0|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14-pro-max/deep-purple.jpg?v=6b5a7bbad0</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -23645,7 +23645,7 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/6c989c2514de5a8d.jpg?v=a4c11f3465|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14-pro-max/gold.jpg?v=26705d95b8</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/6c989c2514de5a8d.jpg?v=7fb05ab043|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14-pro-max/gold.jpg?v=26705d95b8</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -23742,7 +23742,7 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/df9bd48c83d0a6de.jpg?v=4520d0b662|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14-pro-max/gold.jpg?v=26705d95b8</t>
+          <t>https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/_covers/df9bd48c83d0a6de.jpg?v=14ee57057f|https://raw.githubusercontent.com/Rudwwe412/123/main/nn-avito-photos/iphone-14-pro-max/gold.jpg?v=26705d95b8</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
